--- a/sheet/TrapCardData.xlsx
+++ b/sheet/TrapCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0848C6-4AF3-4065-B349-F964CC37AA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F765A2C-B863-4027-8079-8B9A0420592E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5595" yWindow="2910" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -205,10 +205,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时，触发：横置同房间内所有牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>同房间内怪物牌移入或移出时，触发：那张怪物牌点数减2，然后本牌点数减1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -239,6 +235,10 @@
   </si>
   <si>
     <t>回合结束时，触发：选同侧至多1张怪物牌，与本牌一起移动到对侧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时，触发：横置同房间内所有牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -740,7 +740,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>5</v>
@@ -760,7 +760,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>6</v>
@@ -780,7 +780,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>7</v>
@@ -800,7 +800,7 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>30</v>
@@ -818,7 +818,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>31</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>9</v>
@@ -856,7 +856,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>32</v>
@@ -874,7 +874,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>37</v>
@@ -892,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/TrapCardData.xlsx
+++ b/sheet/TrapCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F765A2C-B863-4027-8079-8B9A0420592E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30CEEE2-AF82-43DA-B7D5-DA9A2CC80D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5595" yWindow="2910" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4635" yWindow="3825" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -180,10 +180,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>延迟爆弹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Delayed bomb</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -205,10 +201,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>同房间内怪物牌移入或移出时，触发：那张怪物牌点数减2，然后本牌点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>死亡时，触发：如果本牌点数大于1，则将本牌移动到相邻房间中而不是送墓，然后使本牌和目标房间中所有其他牌点数减1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -229,16 +221,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时：移动1格，然后点数减1。&lt;br&gt;
-点数为0时，触发：消灭同房间1张其他牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>回合结束时，触发：选同侧至多1张怪物牌，与本牌一起移动到对侧。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>回合开始时，触发：横置同房间内所有牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同房间内新增怪物牌时，触发：那张怪物牌点数减2，然后本牌点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>引信炸弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因点数为0而死亡时，触发：消灭场上1张其他牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -663,7 +662,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>34</v>
@@ -680,7 +679,7 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>3</v>
@@ -700,7 +699,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>4</v>
@@ -720,7 +719,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>8</v>
@@ -740,7 +739,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>5</v>
@@ -754,13 +753,13 @@
         <v>22</v>
       </c>
       <c r="B7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>6</v>
@@ -780,7 +779,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>7</v>
@@ -800,7 +799,7 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>30</v>
@@ -818,7 +817,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>31</v>
@@ -836,7 +835,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>9</v>
@@ -856,7 +855,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>32</v>
@@ -865,19 +864,19 @@
     </row>
     <row r="13" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="B13" s="2">
-        <v>2</v>
-      </c>
-      <c r="C13" s="1">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F13" s="4"/>
     </row>
@@ -892,7 +891,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/TrapCardData.xlsx
+++ b/sheet/TrapCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30CEEE2-AF82-43DA-B7D5-DA9A2CC80D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB8F1F7-C392-47D6-B73E-6F484002F69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="3825" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5745" yWindow="3390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -221,10 +221,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时，触发：选同侧至多1张怪物牌，与本牌一起移动到对侧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>回合开始时，触发：横置同房间内所有牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -238,6 +234,10 @@
   </si>
   <si>
     <t>因点数为0而死亡时，触发：消灭场上1张其他牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时，触发：改变本牌势力，然后选同房间至多1张其他怪物牌改变势力。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -739,7 +739,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>5</v>
@@ -759,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>6</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="13" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>36</v>
@@ -891,7 +891,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/TrapCardData.xlsx
+++ b/sheet/TrapCardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB8F1F7-C392-47D6-B73E-6F484002F69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5972C3-EA56-45A3-83EC-F738118D9D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5745" yWindow="3390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3765" yWindow="3765" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -205,10 +205,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>开战时，触发：如果同房间怪物牌合计数量大于1，则将那些怪物牌移入其他房间的同侧，然后消灭本牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>点数降低时，触发：同房间所有牌点数减1，然后消灭本牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -237,7 +233,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时，触发：改变本牌势力，然后选同房间至多1张其他怪物牌改变势力。</t>
+    <t>回合结束时，触发：改变本牌阵营，然后改变同房间至多1张其他怪物牌的阵营。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开战时，触发：如果同房间怪物牌合计数量大于1，则将那些怪物牌逐张移动到其他房间，然后消灭本牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -739,7 +739,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>5</v>
@@ -759,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>6</v>
@@ -799,7 +799,7 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>30</v>
@@ -817,7 +817,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>31</v>
@@ -835,7 +835,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>9</v>
@@ -855,7 +855,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>32</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="13" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>36</v>
@@ -891,7 +891,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/TrapCardData.xlsx
+++ b/sheet/TrapCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5972C3-EA56-45A3-83EC-F738118D9D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E21A2E-D002-4CB2-B330-EE3CE9465145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3765" yWindow="3765" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6435" yWindow="4080" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -128,10 +128,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>传送阵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>爆桶</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -180,64 +176,56 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Delayed bomb</t>
+    <t>传送陷阱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>回合结束时：将主牌堆顶1张牌送墓。&lt;br&gt;
-开战时，触发：用墓地第1张牌替换本牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开战时，触发：同房间所有怪物牌点数变为1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时，触发：如果同房间怪物牌合计数量不小于本牌点数，消灭那些怪物牌，然后消灭本牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时，触发：横置本牌，然后同房间内所有其他牌点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时，触发：如果本牌点数大于1，则将本牌移动到相邻房间中而不是送墓，然后使本牌和目标房间中所有其他牌点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>点数降低时，触发：同房间所有牌点数减1，然后消灭本牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同房间内牌移入或移出时，触发：同房间内所有牌点数减1，然后消灭本牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时，触发：选1个相邻房间，使其中的所有牌点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始时，触发：横置同房间内所有牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同房间内新增怪物牌时，触发：那张怪物牌点数减2，然后本牌点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>引信炸弹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>因点数为0而死亡时，触发：消灭场上1张其他牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时，触发：改变本牌阵营，然后改变同房间至多1张其他怪物牌的阵营。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开战时，触发：如果同房间怪物牌合计数量大于1，则将那些怪物牌逐张移动到其他房间，然后消灭本牌。</t>
+开战时：用墓地第1张牌替换本牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：如果同房间怪物牌合计数量不小于本牌点数，消灭那些怪物牌，然后消灭本牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：横置本牌，然后同房间内所有其他牌点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时：横置同房间内所有牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同房间内新增怪物牌时：那张怪物牌点数减2，然后本牌点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时：如果本牌点数大于1，则本牌免死，将本牌移动到相邻房间，然后使目标房间中所有牌点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开战时：如果同房间怪物牌合计数量大于1，则将那些怪物牌逐张移动到其他房间，然后消灭本牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点数降低时：同房间所有牌点数减1，然后消灭本牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同房间内牌移入或移出时：同房间内所有牌点数减1，然后消灭本牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时：选1个相邻房间，使其中的所有牌点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：改变本牌阵营，然后改变同房间至多1张其他怪物牌的阵营。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续：同房间所有怪物牌点数变为1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -621,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
@@ -639,21 +627,21 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
         <v>27</v>
-      </c>
-      <c r="D1" t="s">
-        <v>28</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -662,10 +650,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -679,7 +667,7 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>3</v>
@@ -699,7 +687,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>4</v>
@@ -713,13 +701,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>8</v>
@@ -739,7 +727,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>5</v>
@@ -759,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>6</v>
@@ -790,7 +778,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
@@ -799,16 +787,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -817,16 +805,16 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
@@ -835,7 +823,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>9</v>
@@ -846,7 +834,7 @@
     </row>
     <row r="12" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -855,16 +843,16 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
@@ -873,25 +861,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/TrapCardData.xlsx
+++ b/sheet/TrapCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E21A2E-D002-4CB2-B330-EE3CE9465145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF825C2-4C37-45BF-9140-E287B6C86E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6435" yWindow="4080" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,17 +50,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Quicksand</t>
-  </si>
-  <si>
     <t>Pitfall</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Cryogas vent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Dart trap</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -77,10 +70,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>① Triggered (Before battle round): Check all rows above this card. If the total card count of a row is greater than the rank of this card, the ranks of all cards in that row are set to one.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>① Triggered (Pre battle): Check the row above this card. If there are more than one card in either column, send all cards in that row to Graveyard. Then send this card to Graveyard as well.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -100,34 +89,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>① Lasting: Negate the effects of { Monster } cards in the row above this card.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>流沙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>落穴</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>尖刺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冷气喷口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>滚石</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>吹箭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>爆桶</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -164,10 +133,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>墓碑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Tomb</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -180,43 +145,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时：将主牌堆顶1张牌送墓。&lt;br&gt;
-开战时：用墓地第1张牌替换本牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时：如果同房间怪物牌合计数量不小于本牌点数，消灭那些怪物牌，然后消灭本牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时：横置本牌，然后同房间内所有其他牌点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始时：横置同房间内所有牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同房间内新增怪物牌时：那张怪物牌点数减2，然后本牌点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时：如果本牌点数大于1，则本牌免死，将本牌移动到相邻房间，然后使目标房间中所有牌点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开战时：如果同房间怪物牌合计数量大于1，则将那些怪物牌逐张移动到其他房间，然后消灭本牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>点数降低时：同房间所有牌点数减1，然后消灭本牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同房间内牌移入或移出时：同房间内所有牌点数减1，然后消灭本牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>死亡时：选1个相邻房间，使其中的所有牌点数减1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -225,7 +153,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>持续：同房间所有怪物牌点数变为1。</t>
+    <t>回合结束时：消灭同房间内所有其他点数与本牌相同的牌，然后本牌点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时：如果本牌点数大于1，则本牌免死，将本牌移动1格，然后使移动后本牌所在房间中所有牌点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同房间内怪物牌移入或移出时：那张怪物牌点数减1，然后本牌点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：如果同房间怪物牌合计数量大于本牌点数，消灭同房间所有牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坟墓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：如果同房间内有敌对牌，则呼唤墓地顶端的1张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开战时：将同房间内1张怪物牌移动到其他房间。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点数降低时：同房间所有牌点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同房间内怪物牌移出后：同房间内所有牌点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吹箭陷阱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尖刺陷阱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -609,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
@@ -627,21 +595,21 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -650,15 +618,15 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -667,18 +635,18 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -687,18 +655,18 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -707,10 +675,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>12</v>
@@ -718,27 +686,27 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2">
         <v>1</v>
@@ -747,38 +715,34 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>15</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
@@ -786,17 +750,19 @@
       <c r="C9" s="1">
         <v>3</v>
       </c>
-      <c r="D9" t="s">
-        <v>42</v>
+      <c r="D9" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -804,17 +770,17 @@
       <c r="C10" s="1">
         <v>3</v>
       </c>
-      <c r="D10" t="s">
-        <v>43</v>
+      <c r="D10" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
@@ -823,45 +789,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/TrapCardData.xlsx
+++ b/sheet/TrapCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF825C2-4C37-45BF-9140-E287B6C86E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35AAE50-1C10-4944-A09F-A72C63F8B98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -66,10 +66,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Mine</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>① Triggered (Pre battle): Check the row above this card. If there are more than one card in either column, send all cards in that row to Graveyard. Then send this card to Graveyard as well.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -77,10 +73,6 @@
     <t>① Triggered (Before battle round): Check all { Monster } cards above this card. Send those with the same rank as this card to Graveyard.</t>
   </si>
   <si>
-    <t>Triggered(Pre battle): Check all { monster } cards in the row above this card and in the same column with this card. If any of them has a rank higher than this card, send all the cards in that row to Graveyard. Then send this card to Graveyard as well.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>① Triggered(On sent to Graveyard from Battlefield): Select cards from below this card with a total rank no higher than this card. Send them to the Graveyard.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -101,10 +93,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>地雷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>石柱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -182,10 +170,6 @@
   </si>
   <si>
     <t>点数降低时：同房间所有牌点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同房间内怪物牌移出后：同房间内所有牌点数减1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -577,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
@@ -595,21 +579,21 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -618,15 +602,15 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -635,18 +619,18 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -655,18 +639,18 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -675,18 +659,18 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -695,18 +679,18 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2">
         <v>1</v>
@@ -715,16 +699,16 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
@@ -733,63 +717,43 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="1">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="2">
-        <v>2</v>
-      </c>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
         <v>25</v>
-      </c>
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
